--- a/Docmentations/SIQs.xlsx
+++ b/Docmentations/SIQs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ITI\iti-Config-managment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ITI\iti-Config-managment\Docmentations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6993FCF-5909-4F0F-9856-8247ED6E6721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7815082-FE87-49AC-8242-FAB54B4D7074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B6544A6E-4D41-4CEF-9174-6A1D4B9FF080}"/>
   </bookViews>
@@ -230,9 +230,6 @@
     <t>each product should have a name, descripton,a picture, price and a purchasing button and add to cart</t>
   </si>
   <si>
-    <t>products and their title and image, search bar, view cart</t>
-  </si>
-  <si>
     <t>LOGIN FEATURE for all type of users</t>
   </si>
   <si>
@@ -256,6 +253,9 @@
   </si>
   <si>
     <t>open on the log in and sign up page then navigate to the home page</t>
+  </si>
+  <si>
+    <t>products and their title and image, view cart</t>
   </si>
 </sst>
 </file>
@@ -850,7 +850,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="9" spans="1:12" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:12" ht="45" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>48</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>25</v>
@@ -1045,10 +1045,10 @@
         <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E18" s="1"/>
     </row>
@@ -1060,7 +1060,7 @@
         <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>25</v>
@@ -1096,13 +1096,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="E22" s="1"/>
     </row>
@@ -1153,7 +1153,7 @@
         <v>41</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>25</v>
